--- a/evals/phase-0.5-probe/scenario/meridian-claims-P0.xlsx
+++ b/evals/phase-0.5-probe/scenario/meridian-claims-P0.xlsx
@@ -8,12 +8,21 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="claim_normalisation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="party_extract" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="vehicle_extract" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="status_snapshot" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="payment_extract" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="fraud_assessment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="claim_header (source)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="policy_dim (lookup)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="fx_rates (lookup)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="claim_fact (target)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="party_dim (target)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="vehicle_dim (target)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="claim_status_snapshot (target)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="payment_fact (target)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="fraud_flag (target)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="claim_normalisation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="party_extract" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="vehicle_extract" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="status_snapshot" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="payment_extract" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="fraud_assessment" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +471,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK, ref claim_fact.claim_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>risk_score</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>is_flagged</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -477,7 +586,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,7 +929,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>enum: none,minor,moderate,severe,total,scratch</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -996,7 +1109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1196,7 +1309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1377,7 +1490,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Map: none-&gt;N, minor-&gt;M, moderate-&gt;M, severe-&gt;S, total-&gt;T</t>
+          <t>Map: none-&gt;N, minor-&gt;M, moderate-&gt;M, severe-&gt;S, total-&gt;T (scratch unhandled)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1425,7 +1538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1588,13 +1701,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1646,27 +1759,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(generated)</t>
+          <t>claim_fact.claim_key</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARCHAR(36)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>payment_id</t>
+          <t>claim_key</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VARCHAR(36)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generate UUID</t>
+          <t>Direct copy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1676,71 +1789,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>ref claim_fact.claim_key</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>claim_fact.claim_key</t>
+          <t>claim_fact.loss_usd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DECIMAL(14,2)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>claim_key</t>
+          <t>paid_amount</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DECIMAL(14,2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Direct copy</t>
+          <t>round 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ref claim_fact.claim_key</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>claim_fact.loss_usd</t>
+          <t>claim_fact.reported_date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DECIMAL(14,2)</t>
+          <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>paid_amount</t>
+          <t>paid_at</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DECIMAL(14,2)</t>
+          <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>round 2</t>
+          <t>to_utc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1749,46 +1858,13 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>claim_fact.reported_date</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_NTZ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>paid_at</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TIMESTAMP_NTZ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>to_utc</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1903,7 +1979,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Score from 0-100 based on claim_fact.party_count and party_dim role distribution</t>
+          <t>multiply 10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1916,10 +1992,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(computed — no source)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>claim_fact.party_count</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>is_flagged</t>
@@ -1932,7 +2012,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>True if risk_score &gt; 70, false otherwise.</t>
+          <t>True if party_count &gt; 7, false otherwise.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1941,6 +2021,1552 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>policy_no</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>claim_type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum: auto, home, life, health</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reported_at</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>incident_at</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>loss_amount</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DECIMAL(14,2)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CHAR(3)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>default USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adjuster_id</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>vehicles[].vin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VARCHAR(17)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vehicles[].make</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VARCHAR(40)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vehicles[].model</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VARCHAR(40)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vehicles[].year</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vehicles[].damage_extent</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>enum: none, minor, moderate, severe, total, scratch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vehicles[].estimate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DECIMAL(12,2)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vehicles[].photos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vehicles[].photos[].photo_id</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VARCHAR(36)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>vehicles[].photos[].angle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>enum: front, rear, left, right, interior</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>parties</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>parties[].party_role</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>parties[].name</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>parties[].contact_phone</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>policy_no</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>policyholder_id</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>effective_date</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>expiry_date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>territory</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CHAR(3)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rate_to_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DECIMAL(10,6)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>policy_ref</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>indexed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>claim_type_code</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VARCHAR(2)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>reported_date</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_NTZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>loss_usd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DECIMAL(14,2)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>loss_source</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vehicle_count</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>party_count</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>max_damage</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>photos[].photo_ref</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VARCHAR(36)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>photos[].view</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adjuster_ref</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>is_open</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rows[].role</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rows[].display_name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rows[].phone_e164</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>list_of record</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nested</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rows[].vin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VARCHAR(17)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rows[].description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rows[].damage_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rows[].estimate_usd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DECIMAL(12,2)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK, ref claim_fact.claim_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>open_flag</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_exposure</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DECIMAL(14,2)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>payment_id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VARCHAR(36)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>claim_key</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ref claim_fact.claim_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>paid_amount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DECIMAL(14,2)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>paid_at</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIMESTAMP_NTZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
